--- a/www/ig/fhir/core/StructureDefinition-fr-core-human-name.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-human-name.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="170">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-19T12:11:47+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,7 +84,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>French profile of datatype HumanName with constraints on prefix and suffix | Profilage du type de données HumanName pour prise en compte de la civilté au niveau de l'élément prefix et du titre au niveau de l'élément suffix</t>
+    <t>Profilage du type de données HumanName pour prise en compte de la civilté au niveau de l'élément prefix et du titre au niveau de l'élément suffix
+.French profile of datatype HumanName with constraints on prefix and suffix</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/HumanName</t>
+    <t>http://hl7.org/fhir/StructureDefinition/HumanName|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -350,7 +351,7 @@
     <t>assemblyOrder</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {humanname-assembly-order}
+    <t xml:space="preserve">Extension {humanname-assembly-order|5.2.0}
 </t>
   </si>
   <si>
@@ -385,7 +386,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/name-use</t>
+    <t>The use of a human name.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
   </si>
   <si>
     <t>XPN.7, but often indicated by which field contains the name</t>
@@ -480,10 +484,10 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>Civilités des personnes physiques du RASS</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J78-Civilite-RASS/FHIR/JDV-J78-Civilite-RASS</t>
+    <t>Civilités des personnes physiques</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J245-Civilite-CISIS/FHIR/JDV-J245-Civilite-CISIS|20230331120000</t>
   </si>
   <si>
     <t>XPN.5</t>
@@ -498,16 +502,10 @@
     <t>HumanName.suffix</t>
   </si>
   <si>
-    <t>jeu de valeurs pour spécifier le titre de la personne</t>
+    <t>Parts that come after the name</t>
   </si>
   <si>
     <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
-  </si>
-  <si>
-    <t>Civilités d'exercice d'un professionnel du RASS</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J79-CiviliteExercice-RASS/FHIR/JDV-J79-CiviliteExercice-RASS</t>
   </si>
   <si>
     <t>XPN/4</t>
@@ -851,44 +849,44 @@
   <dimension ref="A1:AM12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.7265625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="21.7890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.3984375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="12.609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="30.81640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="18.796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="37.70703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="37.1171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="92.578125" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="79.859375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="42.4609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="90.6875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="18.8046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="26.78515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="82.01953125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="16.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="54.296875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="29.57421875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="24.18359375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="46.8359375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="25.51171875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="20.859375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1519,9 +1517,11 @@
       <c r="X6" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="Y6" s="2"/>
+      <c r="Y6" t="s" s="2">
+        <v>120</v>
+      </c>
       <c r="Z6" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -1554,21 +1554,21 @@
         <v>85</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1594,16 +1594,16 @@
         <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O7" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P7" t="s" s="2">
         <v>77</v>
@@ -1652,7 +1652,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -1667,10 +1667,10 @@
         <v>85</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -1678,14 +1678,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -1707,13 +1707,13 @@
         <v>91</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1763,7 +1763,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -1778,25 +1778,25 @@
         <v>85</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -1818,13 +1818,13 @@
         <v>91</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1874,7 +1874,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -1889,21 +1889,21 @@
         <v>85</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1929,10 +1929,10 @@
         <v>91</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1959,13 +1959,13 @@
         <v>77</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>77</v>
@@ -1983,7 +1983,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -1998,21 +1998,21 @@
         <v>85</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2038,10 +2038,10 @@
         <v>91</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2068,13 +2068,13 @@
         <v>77</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>77</v>
@@ -2092,7 +2092,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2107,10 +2107,10 @@
         <v>85</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AL11" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AL11" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2144,17 +2144,17 @@
         <v>113</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2203,7 +2203,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2218,13 +2218,13 @@
         <v>85</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AM12" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-human-name.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-human-name.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="171">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.2.0</t>
+    <t>2.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T12:11:47+01:00</t>
+    <t>2024-09-04T10:06:33+02:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(Work))</t>
+    <t>Interop'Santé (http://interopsante.org/)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,8 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Profilage du type de données HumanName pour prise en compte de la civilté au niveau de l'élément prefix et du titre au niveau de l'élément suffix
-.French profile of datatype HumanName with constraints on prefix and suffix</t>
+    <t>French profile of datatype HumanName with constraints on prefix and suffix | Profilage du type de données HumanName pour prise en compte de la civilté au niveau de l'élément prefix et du titre au niveau de l'élément suffix</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -115,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/HumanName|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/HumanName</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -351,7 +350,7 @@
     <t>assemblyOrder</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {humanname-assembly-order|5.2.0}
+    <t xml:space="preserve">Extension {humanname-assembly-order}
 </t>
   </si>
   <si>
@@ -386,10 +385,7 @@
     <t>required</t>
   </si>
   <si>
-    <t>The use of a human name.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/name-use</t>
   </si>
   <si>
     <t>XPN.7, but often indicated by which field contains the name</t>
@@ -484,10 +480,10 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>Civilités des personnes physiques</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J245-Civilite-CISIS/FHIR/JDV-J245-Civilite-CISIS|20230331120000</t>
+    <t>Civilités des personnes physiques du RASS</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J78-Civilite-RASS/FHIR/JDV-J78-Civilite-RASS</t>
   </si>
   <si>
     <t>XPN.5</t>
@@ -502,10 +498,16 @@
     <t>HumanName.suffix</t>
   </si>
   <si>
-    <t>Parts that come after the name</t>
+    <t>jeu de valeurs pour spécifier le titre de la personne</t>
   </si>
   <si>
     <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
+  </si>
+  <si>
+    <t>Civilités d'exercice d'un professionnel du RASS</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J79-CiviliteExercice-RASS/FHIR/JDV-J79-CiviliteExercice-RASS</t>
   </si>
   <si>
     <t>XPN/4</t>
@@ -849,44 +851,44 @@
   <dimension ref="A1:AM12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="30.81640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="18.796875" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="12.421875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="10.875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="35.7265625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="21.7890625" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.3984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="12.609375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="37.1171875" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="37.70703125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="79.859375" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="92.578125" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="26.78515625" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="82.01953125" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="16.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="42.4609375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="90.6875" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="18.8046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="46.8359375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="25.51171875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="20.859375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="54.296875" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="29.57421875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="24.18359375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1517,11 +1519,9 @@
       <c r="X6" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="Y6" t="s" s="2">
+      <c r="Y6" s="2"/>
+      <c r="Z6" t="s" s="2">
         <v>120</v>
-      </c>
-      <c r="Z6" t="s" s="2">
-        <v>121</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -1554,21 +1554,21 @@
         <v>85</v>
       </c>
       <c r="AK6" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="AL6" t="s" s="2">
         <v>122</v>
       </c>
-      <c r="AL6" t="s" s="2">
+      <c r="AM6" t="s" s="2">
         <v>123</v>
-      </c>
-      <c r="AM6" t="s" s="2">
-        <v>124</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1594,16 +1594,16 @@
         <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
+        <v>125</v>
+      </c>
+      <c r="M7" t="s" s="2">
         <v>126</v>
       </c>
-      <c r="M7" t="s" s="2">
+      <c r="N7" t="s" s="2">
         <v>127</v>
       </c>
-      <c r="N7" t="s" s="2">
+      <c r="O7" t="s" s="2">
         <v>128</v>
-      </c>
-      <c r="O7" t="s" s="2">
-        <v>129</v>
       </c>
       <c r="P7" t="s" s="2">
         <v>77</v>
@@ -1652,7 +1652,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -1667,10 +1667,10 @@
         <v>85</v>
       </c>
       <c r="AK7" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="AL7" t="s" s="2">
         <v>130</v>
-      </c>
-      <c r="AL7" t="s" s="2">
-        <v>131</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -1678,14 +1678,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -1707,13 +1707,13 @@
         <v>91</v>
       </c>
       <c r="L8" t="s" s="2">
+        <v>133</v>
+      </c>
+      <c r="M8" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="M8" t="s" s="2">
+      <c r="N8" t="s" s="2">
         <v>135</v>
-      </c>
-      <c r="N8" t="s" s="2">
-        <v>136</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1763,7 +1763,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -1778,25 +1778,25 @@
         <v>85</v>
       </c>
       <c r="AK8" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="AL8" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="AL8" t="s" s="2">
+      <c r="AM8" t="s" s="2">
         <v>138</v>
-      </c>
-      <c r="AM8" t="s" s="2">
-        <v>139</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -1818,13 +1818,13 @@
         <v>91</v>
       </c>
       <c r="L9" t="s" s="2">
+        <v>141</v>
+      </c>
+      <c r="M9" t="s" s="2">
         <v>142</v>
       </c>
-      <c r="M9" t="s" s="2">
+      <c r="N9" t="s" s="2">
         <v>143</v>
-      </c>
-      <c r="N9" t="s" s="2">
-        <v>144</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1874,7 +1874,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -1889,21 +1889,21 @@
         <v>85</v>
       </c>
       <c r="AK9" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="AL9" t="s" s="2">
         <v>145</v>
       </c>
-      <c r="AL9" t="s" s="2">
+      <c r="AM9" t="s" s="2">
         <v>146</v>
-      </c>
-      <c r="AM9" t="s" s="2">
-        <v>147</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1929,10 +1929,10 @@
         <v>91</v>
       </c>
       <c r="L10" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="M10" t="s" s="2">
         <v>149</v>
-      </c>
-      <c r="M10" t="s" s="2">
-        <v>150</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1959,14 +1959,14 @@
         <v>77</v>
       </c>
       <c r="X10" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="Y10" t="s" s="2">
         <v>151</v>
       </c>
-      <c r="Y10" t="s" s="2">
+      <c r="Z10" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="Z10" t="s" s="2">
-        <v>153</v>
-      </c>
       <c r="AA10" t="s" s="2">
         <v>77</v>
       </c>
@@ -1983,7 +1983,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -1998,21 +1998,21 @@
         <v>85</v>
       </c>
       <c r="AK10" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="AL10" t="s" s="2">
         <v>154</v>
       </c>
-      <c r="AL10" t="s" s="2">
+      <c r="AM10" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="AM10" t="s" s="2">
-        <v>156</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2038,10 +2038,10 @@
         <v>91</v>
       </c>
       <c r="L11" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="M11" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="M11" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2068,13 +2068,13 @@
         <v>77</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>77</v>
+        <v>159</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>77</v>
+        <v>160</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>77</v>
@@ -2092,7 +2092,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2107,10 +2107,10 @@
         <v>85</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2144,17 +2144,17 @@
         <v>113</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2203,7 +2203,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2218,13 +2218,13 @@
         <v>85</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>

--- a/www/ig/fhir/core/StructureDefinition-fr-core-human-name.xlsx
+++ b/www/ig/fhir/core/StructureDefinition-fr-core-human-name.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="170">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.1.0</t>
+    <t>2.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-09-04T10:06:33+02:00</t>
+    <t>2026-03-25T18:08:32+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -69,10 +69,10 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Interop'Santé (http://interopsante.org/)</t>
-  </si>
-  <si>
-    <t>InteropSanté (fhir@interopsante.org(work))</t>
+    <t>Interop'Santé (http://interopsante.org)</t>
+  </si>
+  <si>
+    <t>InteropSanté (fhir@interopsante.org(Work))</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -84,7 +84,8 @@
     <t>Description</t>
   </si>
   <si>
-    <t>French profile of datatype HumanName with constraints on prefix and suffix | Profilage du type de données HumanName pour prise en compte de la civilté au niveau de l'élément prefix et du titre au niveau de l'élément suffix</t>
+    <t>Profilage du type de données HumanName pour prise en compte de la civilté au niveau de l'élément prefix et du titre au niveau de l'élément suffix
+.French profile of datatype HumanName with constraints on prefix and suffix</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -114,7 +115,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/HumanName</t>
+    <t>http://hl7.org/fhir/StructureDefinition/HumanName|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -350,7 +351,7 @@
     <t>assemblyOrder</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {humanname-assembly-order}
+    <t xml:space="preserve">Extension {humanname-assembly-order|5.2.0}
 </t>
   </si>
   <si>
@@ -385,7 +386,10 @@
     <t>required</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/name-use</t>
+    <t>The use of a human name.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/name-use|4.0.1</t>
   </si>
   <si>
     <t>XPN.7, but often indicated by which field contains the name</t>
@@ -480,10 +484,10 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>Civilités des personnes physiques du RASS</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J78-Civilite-RASS/FHIR/JDV-J78-Civilite-RASS</t>
+    <t>Civilités des personnes physiques</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J245-Civilite-CISIS/FHIR/JDV-J245-Civilite-CISIS|20230331120000</t>
   </si>
   <si>
     <t>XPN.5</t>
@@ -498,16 +502,10 @@
     <t>HumanName.suffix</t>
   </si>
   <si>
-    <t>jeu de valeurs pour spécifier le titre de la personne</t>
+    <t>Parts that come after the name</t>
   </si>
   <si>
     <t>Part of the name that is acquired as a title due to academic, legal, employment or nobility status, etc. and that appears at the end of the name.</t>
-  </si>
-  <si>
-    <t>Civilités d'exercice d'un professionnel du RASS</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J79-CiviliteExercice-RASS/FHIR/JDV-J79-CiviliteExercice-RASS</t>
   </si>
   <si>
     <t>XPN/4</t>
@@ -851,44 +849,44 @@
   <dimension ref="A1:AM12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="35.7265625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="21.7890625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="14.3984375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="12.609375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.1484375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.58203125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="4.94140625" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.7109375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="12.1875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="30.81640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="18.796875" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="12.421875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.30078125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="3.953125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.265625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="37.70703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="37.1171875" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="92.578125" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="79.859375" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="9.04296875" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.77734375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.13671875" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.40234375" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.9609375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="42.4609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="90.6875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.8828125" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="20.84375" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="40.0859375" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="15.703125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="13.125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="18.8046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.53125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="7.80078125" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="13.609375" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="13.91796875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="15.01171875" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="14.62890625" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="26.78515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="82.01953125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.07421875" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="17.98046875" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="34.578125" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="13.54296875" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="11.3203125" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="16.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="8.22265625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="8.53125" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="54.296875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="29.57421875" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="24.18359375" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="46.8359375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="25.51171875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="20.859375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1519,9 +1517,11 @@
       <c r="X6" t="s" s="2">
         <v>119</v>
       </c>
-      <c r="Y6" s="2"/>
+      <c r="Y6" t="s" s="2">
+        <v>120</v>
+      </c>
       <c r="Z6" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>77</v>
@@ -1554,21 +1554,21 @@
         <v>85</v>
       </c>
       <c r="AK6" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AL6" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AM6" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1594,16 +1594,16 @@
         <v>91</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O7" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="P7" t="s" s="2">
         <v>77</v>
@@ -1652,7 +1652,7 @@
         <v>77</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>78</v>
@@ -1667,10 +1667,10 @@
         <v>85</v>
       </c>
       <c r="AK7" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>77</v>
@@ -1678,14 +1678,14 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
@@ -1707,13 +1707,13 @@
         <v>91</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -1763,7 +1763,7 @@
         <v>77</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>78</v>
@@ -1778,25 +1778,25 @@
         <v>85</v>
       </c>
       <c r="AK8" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AM8" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
@@ -1818,13 +1818,13 @@
         <v>91</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N9" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O9" s="2"/>
       <c r="P9" t="s" s="2">
@@ -1874,7 +1874,7 @@
         <v>77</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>78</v>
@@ -1889,21 +1889,21 @@
         <v>85</v>
       </c>
       <c r="AK9" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AL9" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AM9" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1929,10 +1929,10 @@
         <v>91</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1959,13 +1959,13 @@
         <v>77</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>77</v>
@@ -1983,7 +1983,7 @@
         <v>77</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>78</v>
@@ -1998,21 +1998,21 @@
         <v>85</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="AL10" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AM10" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -2038,10 +2038,10 @@
         <v>91</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2068,13 +2068,13 @@
         <v>77</v>
       </c>
       <c r="X11" t="s" s="2">
-        <v>150</v>
+        <v>77</v>
       </c>
       <c r="Y11" t="s" s="2">
-        <v>159</v>
+        <v>77</v>
       </c>
       <c r="Z11" t="s" s="2">
-        <v>160</v>
+        <v>77</v>
       </c>
       <c r="AA11" t="s" s="2">
         <v>77</v>
@@ -2092,7 +2092,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2107,10 +2107,10 @@
         <v>85</v>
       </c>
       <c r="AK11" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AL11" t="s" s="2">
         <v>161</v>
-      </c>
-      <c r="AL11" t="s" s="2">
-        <v>162</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>77</v>
@@ -2118,10 +2118,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2144,17 +2144,17 @@
         <v>113</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="L12" t="s" s="2">
+      <c r="M12" t="s" s="2">
         <v>165</v>
-      </c>
-      <c r="M12" t="s" s="2">
-        <v>166</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2203,7 +2203,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2218,13 +2218,13 @@
         <v>85</v>
       </c>
       <c r="AK12" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="AL12" t="s" s="2">
         <v>168</v>
       </c>
-      <c r="AL12" t="s" s="2">
+      <c r="AM12" t="s" s="2">
         <v>169</v>
-      </c>
-      <c r="AM12" t="s" s="2">
-        <v>170</v>
       </c>
     </row>
   </sheetData>
